--- a/mealkart-backend/mealkart_orders.xlsx
+++ b/mealkart-backend/mealkart_orders.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -665,9 +665,53 @@
         <v>confirmed</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>MK68975333389O</v>
+      </c>
+      <c r="B8" t="str">
+        <v>29/3/2026, 1:06:22 pm</v>
+      </c>
+      <c r="C8" t="str">
+        <v>The International School Bangalore (TISB)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>One Meal</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Srini</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Class 3</v>
+      </c>
+      <c r="G8" t="str">
+        <v>D</v>
+      </c>
+      <c r="H8" t="str">
+        <v>None</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Krishna</v>
+      </c>
+      <c r="J8" t="str">
+        <v>+919566680245</v>
+      </c>
+      <c r="K8" t="str">
+        <v>pay_SWxeB9qqRsQH7a</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8">
+        <v>120</v>
+      </c>
+      <c r="N8" t="str">
+        <v>confirmed</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N8"/>
   </ignoredErrors>
 </worksheet>
 </file>